--- a/exams/risultati_scritto_2026_01_09_e_27.xlsx
+++ b/exams/risultati_scritto_2026_01_09_e_27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t004672\AppData\Local\finance_course\exams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7479B2DA-9D3E-49C8-9232-A4F2F9A892B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9327C982-88A5-40BC-A8E6-16216AAF396E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2385" yWindow="1455" windowWidth="24285" windowHeight="13425" activeTab="1" xr2:uid="{6CFE4764-E1FB-4DB6-AB83-5FACA4F3BFDE}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{6CFE4764-E1FB-4DB6-AB83-5FACA4F3BFDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1405,7 +1405,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -1413,7 +1413,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1">
         <f>AVERAGE(C21:J21)</f>
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="12">
-        <f t="shared" ref="C24:J24" si="6">SUMPRODUCT(C18:C23,$A18:$A23)/6</f>
+        <f t="shared" ref="C24:F24" si="6">SUMPRODUCT(C18:C23,$A18:$A23)/6</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="D24" s="12">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="F24" s="12">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
@@ -1504,7 +1504,7 @@
         <v>0.75</v>
       </c>
       <c r="C25" s="1">
-        <f t="shared" ref="C25:J25" si="7">+$B$9*C24+(1-$B$9)*C26</f>
+        <f t="shared" ref="C25:F25" si="7">+$B$9*C24+(1-$B$9)*C26</f>
         <v>8</v>
       </c>
       <c r="D25" s="1">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F25" s="1">
         <f t="shared" si="7"/>
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
